--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488053_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488053_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2395</v>
+        <v>6.4901</v>
       </c>
       <c r="E2" t="n">
-        <v>9.940099999999999</v>
+        <v>8.1065</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7007</v>
+        <v>-1.6164</v>
       </c>
       <c r="G2" t="n">
         <v>2.0087</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5766</v>
+        <v>1.8272</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2746</v>
+        <v>1.441</v>
       </c>
       <c r="U2" t="n">
-        <v>0.302</v>
+        <v>0.3862</v>
       </c>
       <c r="V2" t="n">
         <v>0.8701</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.163500000000001</v>
+        <v>5.9687</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4764</v>
+        <v>4.1521</v>
       </c>
       <c r="F3" t="n">
-        <v>2.687</v>
+        <v>1.8166</v>
       </c>
       <c r="G3" t="n">
         <v>1.2479</v>
@@ -688,13 +688,13 @@
         <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>3.975</v>
+        <v>1.7803</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7806</v>
+        <v>0.4563</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1945</v>
+        <v>1.324</v>
       </c>
       <c r="V3" t="n">
         <v>2.1476</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0334</v>
+        <v>4.1633</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0467</v>
+        <v>3.1485</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9867</v>
+        <v>1.0148</v>
       </c>
       <c r="G5" t="n">
         <v>3.7027</v>
@@ -844,13 +844,13 @@
         <v>0.1982</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1325</v>
+        <v>0.2624</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5693</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6286</v>
+        <v>1.9551</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1581</v>
+        <v>2.2599</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5295</v>
+        <v>-0.3048</v>
       </c>
       <c r="G6" t="n">
         <v>2.3299</v>
@@ -922,13 +922,13 @@
         <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9023</v>
+        <v>1.2288</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3085</v>
+        <v>0.4104</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5938</v>
+        <v>0.8184</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2071</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7762</v>
+        <v>1.3208</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8066</v>
+        <v>1.5196</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0303</v>
+        <v>-0.1988</v>
       </c>
       <c r="G7" t="n">
         <v>0.8991</v>
@@ -1000,13 +1000,13 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3033</v>
+        <v>0.2413</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0608</v>
+        <v>-0.3477</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7575</v>
+        <v>0.589</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2071</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5727</v>
+        <v>0.8182</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4712</v>
+        <v>0.7513</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1016</v>
+        <v>0.0669</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0444</v>
@@ -1078,13 +1078,13 @@
         <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7026</v>
+        <v>0.6883</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9873</v>
+        <v>0.2351</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2847</v>
+        <v>0.4532</v>
       </c>
       <c r="V8" t="n">
         <v>3.3547</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.626</v>
+        <v>0.7962</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2971</v>
+        <v>0.6197</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3289</v>
+        <v>0.1765</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1981</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4963</v>
+        <v>0.926</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4881</v>
+        <v>0.4287</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0081</v>
+        <v>0.4973</v>
       </c>
       <c r="V9" t="n">
         <v>0.2666</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9686</v>
+        <v>-0.8386</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1178</v>
+        <v>-0.0159</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8508</v>
+        <v>-0.8227</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5285</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0437</v>
+        <v>0.0863</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V10" t="n">
         <v>0.6036</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5521</v>
+        <v>-2.1341</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.2231</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0233</v>
+        <v>-1.911</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0263</v>
@@ -1312,13 +1312,13 @@
         <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0609</v>
+        <v>0.357</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.312</v>
+        <v>-0.0064</v>
       </c>
       <c r="U11" t="n">
-        <v>0.251</v>
+        <v>0.3634</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8701</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.526</v>
+        <v>-6.944</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1631</v>
+        <v>-5.4687</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3629</v>
+        <v>-1.4752</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8683</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5733</v>
+        <v>1.1554</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9949</v>
+        <v>0.6893</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5784</v>
+        <v>0.4661</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4737</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4225</v>
+        <v>16.4224</v>
       </c>
       <c r="E13" t="n">
-        <v>19.6767</v>
+        <v>19.67660000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2543</v>
+        <v>-3.2541</v>
       </c>
       <c r="G13" t="n">
         <v>9.349400000000001</v>
@@ -1468,13 +1468,13 @@
         <v>9.911099999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>8.552900000000001</v>
+        <v>8.552999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>3.011200000000001</v>
+        <v>3.011299999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>5.5418</v>
+        <v>5.541700000000001</v>
       </c>
       <c r="V13" t="n">
         <v>2.4846</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5923</v>
+        <v>1.1909</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3654</v>
+        <v>4.2449</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7731</v>
+        <v>-3.0539</v>
       </c>
       <c r="G14" t="n">
         <v>2.914</v>
@@ -1546,13 +1546,13 @@
         <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4096</v>
+        <v>0.0083</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2997</v>
+        <v>0.1791</v>
       </c>
       <c r="U14" t="n">
-        <v>0.11</v>
+        <v>-0.1708</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1367</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4229</v>
+        <v>0.5809</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.022</v>
+        <v>0.0798</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4449</v>
+        <v>0.5011</v>
       </c>
       <c r="G15" t="n">
         <v>0.5837</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1608</v>
+        <v>-0.0028</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6364</v>
+        <v>-0.5006</v>
       </c>
       <c r="E16" t="n">
         <v>0.5796</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.216</v>
+        <v>-1.0802</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7612</v>
@@ -1702,13 +1702,13 @@
         <v>0.3964</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2717</v>
+        <v>-0.1358</v>
       </c>
       <c r="T16" t="n">
         <v>0.1358</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4075</v>
+        <v>-0.2717</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2103</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5899</v>
+        <v>0.6917</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8001</v>
+        <v>-1.6036</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8421</v>
@@ -1780,13 +1780,13 @@
         <v>0.1982</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5664</v>
+        <v>-0.2679</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4257</v>
+        <v>-0.3239</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1406</v>
+        <v>0.0559</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4399</v>
+        <v>-0.9246</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8163</v>
+        <v>1.2238</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2562</v>
+        <v>-2.1484</v>
       </c>
       <c r="G18" t="n">
         <v>0.149</v>
@@ -1858,13 +1858,13 @@
         <v>2.5769</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8138</v>
+        <v>-1.2985</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2369</v>
+        <v>-0.8294</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5768</v>
+        <v>-0.4691</v>
       </c>
       <c r="V18" t="n">
         <v>1.8107</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.871</v>
+        <v>-1.4015</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4746</v>
+        <v>1.7802</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3456</v>
+        <v>-3.1817</v>
       </c>
       <c r="G19" t="n">
         <v>-0.082</v>
@@ -1936,13 +1936,13 @@
         <v>2.1805</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.4958</v>
+        <v>-2.0263</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4131</v>
+        <v>-1.1075</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0827</v>
+        <v>-0.9188</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4737</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7522</v>
+        <v>-3.0297</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-1.0984</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9594</v>
+        <v>-1.9313</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4788</v>
@@ -2014,13 +2014,13 @@
         <v>0.5947</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2822</v>
+        <v>-0.5598</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2458</v>
+        <v>-0.5514</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0364</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0.6036</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4311</v>
+        <v>-3.0426</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1234</v>
+        <v>-1.2804</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3076</v>
+        <v>-1.7623</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.755</v>
+        <v>-2.4017</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7161</v>
+        <v>-0.2933</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.4711</v>
+        <v>-2.1084</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4456</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5075</v>
+        <v>-0.1072</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9531</v>
+        <v>0.0078</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3094</v>
+        <v>-2.3023</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7914</v>
+        <v>-0.1861</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.518</v>
+        <v>-2.1162</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9911</v>
+        <v>1.9822</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4559</v>
+        <v>-1.416</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8808</v>
+        <v>-1.1809</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4249</v>
+        <v>-0.2351</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2112</v>
+        <v>-1.2071</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3923</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6036</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4605</v>
+        <v>-3.734</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.586</v>
+        <v>-2.2253</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8746</v>
+        <v>-1.5088</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4017</v>
+        <v>-3.755</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2933</v>
+        <v>0.7161</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1084</v>
+        <v>-4.4711</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.4456</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1072</v>
+        <v>1.5075</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0078</v>
+        <v>-1.9531</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3023</v>
+        <v>-3.3094</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1861</v>
+        <v>-0.7914</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1162</v>
+        <v>-2.518</v>
       </c>
       <c r="P22" t="n">
-        <v>1.9822</v>
+        <v>0.9911</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9822</v>
+        <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8339</v>
+        <v>-0.7589</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4865</v>
+        <v>-0.9827</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3474</v>
+        <v>0.2237</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2071</v>
+        <v>-0.2112</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3923</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2071</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6363</v>
+        <v>-3.9702</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0474</v>
+        <v>-0.7418</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5889</v>
+        <v>-3.2285</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6752</v>
@@ -2248,13 +2248,13 @@
         <v>2.1805</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0821</v>
+        <v>-1.416</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2259</v>
+        <v>-0.9203</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8562</v>
+        <v>-0.4957</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8701</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-16.4225</v>
+        <v>-15.7432</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2542</v>
+        <v>3.2541</v>
       </c>
       <c r="F24" t="n">
-        <v>-19.6766</v>
+        <v>-18.9976</v>
       </c>
       <c r="G24" t="n">
         <v>-9.349299999999999</v>
@@ -2305,13 +2305,13 @@
         <v>13.6572</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1708999999999994</v>
+        <v>-0.1708999999999996</v>
       </c>
       <c r="M24" t="n">
         <v>-22.8356</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.284899999999999</v>
+        <v>-6.2849</v>
       </c>
       <c r="O24" t="n">
         <v>-16.5506</v>
@@ -2326,19 +2326,19 @@
         <v>13.8757</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.553000000000001</v>
+        <v>-7.873699999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.5416</v>
+        <v>-5.541700000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.0111</v>
+        <v>-2.3322</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4845</v>
       </c>
       <c r="W24" t="n">
-        <v>5.220800000000001</v>
+        <v>5.2208</v>
       </c>
       <c r="X24" t="n">
         <v>-7.7055</v>
